--- a/data/trans_dic/P6902-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,5; 30,26</t>
+          <t>11,46; 30,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,24; 47,27</t>
+          <t>25,78; 47,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,4; 56,89</t>
+          <t>28,43; 56,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,49; 57,19</t>
+          <t>31,16; 57,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,62; 58,77</t>
+          <t>26,25; 60,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,11; 71,16</t>
+          <t>35,94; 70,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,22; 65,2</t>
+          <t>27,47; 64,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,28; 69,67</t>
+          <t>49,38; 71,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,72; 34,89</t>
+          <t>18,67; 34,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,92; 51,28</t>
+          <t>31,69; 51,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,3; 55,17</t>
+          <t>32,52; 54,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,92; 59,56</t>
+          <t>41,87; 59,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,57; 51,39</t>
+          <t>34,86; 51,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,41; 60,92</t>
+          <t>39,69; 60,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,41; 54,23</t>
+          <t>33,16; 54,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,6; 63,68</t>
+          <t>44,0; 63,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,32; 59,87</t>
+          <t>32,39; 59,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,67; 70,92</t>
+          <t>43,3; 68,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,49; 66,75</t>
+          <t>39,55; 66,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,4; 71,62</t>
+          <t>55,36; 71,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,79; 51,51</t>
+          <t>36,7; 51,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,16; 62,04</t>
+          <t>45,33; 61,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,01; 54,37</t>
+          <t>37,95; 55,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,68; 65,35</t>
+          <t>51,51; 64,96</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,35; 53,17</t>
+          <t>33,28; 53,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,29; 64,41</t>
+          <t>40,33; 65,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,49; 43,15</t>
+          <t>24,28; 42,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,5; 78,29</t>
+          <t>51,63; 78,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,15; 79,51</t>
+          <t>51,09; 78,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,0; 68,06</t>
+          <t>40,65; 68,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,26; 76,16</t>
+          <t>52,62; 76,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,55; 75,15</t>
+          <t>18,79; 75,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,54; 59,0</t>
+          <t>41,17; 57,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,79; 61,09</t>
+          <t>42,44; 61,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,55; 52,48</t>
+          <t>37,03; 52,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,75; 72,43</t>
+          <t>28,29; 71,73</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,65; 65,94</t>
+          <t>49,01; 65,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,89; 59,24</t>
+          <t>36,55; 58,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,23; 68,02</t>
+          <t>46,91; 68,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71,63; 87,59</t>
+          <t>71,11; 86,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,52; 61,59</t>
+          <t>40,49; 62,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,35; 73,19</t>
+          <t>48,53; 75,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,3; 80,25</t>
+          <t>54,71; 79,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,41; 78,44</t>
+          <t>56,36; 78,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,14; 61,32</t>
+          <t>48,0; 61,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,0; 62,44</t>
+          <t>45,85; 63,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,4; 69,86</t>
+          <t>54,33; 69,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,27; 81,14</t>
+          <t>67,86; 80,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>38,71; 48,01</t>
+          <t>39,26; 48,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,96; 52,55</t>
+          <t>41,42; 52,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,8; 48,77</t>
+          <t>37,98; 49,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56,4; 67,04</t>
+          <t>56,08; 67,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,02; 58,75</t>
+          <t>44,37; 57,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,04; 64,04</t>
+          <t>49,92; 64,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,61; 67,05</t>
+          <t>53,8; 66,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,3; 68,86</t>
+          <t>42,76; 68,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,18; 49,68</t>
+          <t>42,3; 49,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,69; 55,53</t>
+          <t>46,55; 55,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,38; 54,22</t>
+          <t>45,73; 54,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,16; 66,32</t>
+          <t>50,36; 65,77</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9123; 24003</t>
+          <t>9092; 24302</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20092; 36201</t>
+          <t>19744; 36053</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16072; 31103</t>
+          <t>15546; 30908</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22426; 40726</t>
+          <t>22189; 40788</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8581; 18947</t>
+          <t>8465; 19509</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13082; 25088</t>
+          <t>12669; 24695</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8741; 19506</t>
+          <t>8217; 19380</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25853; 38098</t>
+          <t>27003; 38982</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19766; 38926</t>
+          <t>20829; 38920</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36820; 57352</t>
+          <t>35435; 57687</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27325; 46666</t>
+          <t>27511; 46492</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51521; 74990</t>
+          <t>52715; 75066</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50472; 75023</t>
+          <t>50884; 75509</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37004; 55781</t>
+          <t>36341; 55512</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31435; 52595</t>
+          <t>32161; 52714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48823; 71311</t>
+          <t>49277; 71561</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17062; 31611</t>
+          <t>17103; 31267</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29000; 45036</t>
+          <t>27493; 43532</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21935; 37082</t>
+          <t>21968; 37123</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54692; 70715</t>
+          <t>54660; 70983</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73130; 102390</t>
+          <t>72946; 102304</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70026; 96195</t>
+          <t>70292; 95761</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57982; 82931</t>
+          <t>57892; 84439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>108905; 137702</t>
+          <t>108539; 136881</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35564; 58458</t>
+          <t>36584; 58302</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31256; 51241</t>
+          <t>32084; 52053</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26919; 47439</t>
+          <t>26694; 47023</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28466; 43274</t>
+          <t>28540; 43525</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23803; 36998</t>
+          <t>23776; 36663</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21193; 36060</t>
+          <t>21537; 36340</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33188; 49314</t>
+          <t>34068; 49516</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18942; 72822</t>
+          <t>18207; 72813</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64995; 92319</t>
+          <t>64418; 90022</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58031; 80967</t>
+          <t>56254; 81693</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65590; 91675</t>
+          <t>64684; 91272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39182; 110232</t>
+          <t>43053; 109154</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66676; 90365</t>
+          <t>67173; 89251</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28554; 45853</t>
+          <t>28288; 45332</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41752; 60133</t>
+          <t>41472; 60260</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72363; 88491</t>
+          <t>71844; 87701</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35878; 54538</t>
+          <t>35858; 55059</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30993; 46913</t>
+          <t>31107; 48096</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37205; 53031</t>
+          <t>36151; 52410</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>59649; 81491</t>
+          <t>58555; 81070</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>108614; 138333</t>
+          <t>108283; 139823</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63671; 88347</t>
+          <t>64873; 89614</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>84039; 107932</t>
+          <t>83938; 107273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>137864; 166274</t>
+          <t>139071; 165682</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>182842; 226766</t>
+          <t>185412; 229307</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>133156; 170842</t>
+          <t>134651; 170371</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132290; 170699</t>
+          <t>132941; 171739</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>191466; 227618</t>
+          <t>190398; 227815</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99095; 129325</t>
+          <t>97668; 126680</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>108010; 138217</t>
+          <t>107731; 138490</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>115947; 145027</t>
+          <t>116377; 144767</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>149821; 243927</t>
+          <t>151457; 241655</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>292085; 343979</t>
+          <t>292908; 345489</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>252559; 300396</t>
+          <t>251828; 299706</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>256966; 307060</t>
+          <t>258995; 307871</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>354902; 460070</t>
+          <t>349388; 456275</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6902-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 30,63</t>
+          <t>11,4; 29,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,78; 47,08</t>
+          <t>26,25; 47,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,43; 56,53</t>
+          <t>25,39; 54,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,16; 57,27</t>
+          <t>32,64; 59,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,25; 60,51</t>
+          <t>27,03; 58,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,94; 70,05</t>
+          <t>36,16; 72,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,47; 64,78</t>
+          <t>27,28; 63,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,38; 71,29</t>
+          <t>50,35; 70,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 34,88</t>
+          <t>18,13; 35,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,69; 51,58</t>
+          <t>33,15; 52,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,52; 54,96</t>
+          <t>31,81; 54,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,87; 59,63</t>
+          <t>43,84; 61,95</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>60,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,86; 51,72</t>
+          <t>35,3; 51,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,69; 60,63</t>
+          <t>40,68; 61,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,16; 54,35</t>
+          <t>33,17; 54,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,0; 63,9</t>
+          <t>48,46; 67,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,39; 59,22</t>
+          <t>31,8; 58,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,3; 68,56</t>
+          <t>42,68; 68,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,55; 66,83</t>
+          <t>38,96; 65,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,36; 71,9</t>
+          <t>55,67; 71,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,7; 51,47</t>
+          <t>37,12; 51,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,33; 61,76</t>
+          <t>45,11; 61,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37,95; 55,36</t>
+          <t>38,8; 55,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,51; 64,96</t>
+          <t>54,16; 66,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,28; 53,03</t>
+          <t>32,93; 52,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,33; 65,43</t>
+          <t>41,11; 64,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,28; 42,77</t>
+          <t>24,49; 43,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,63; 78,74</t>
+          <t>45,09; 72,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,09; 78,79</t>
+          <t>49,41; 78,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,65; 68,59</t>
+          <t>40,21; 68,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,62; 76,48</t>
+          <t>53,05; 76,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,79; 75,14</t>
+          <t>60,21; 79,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41,17; 57,53</t>
+          <t>41,65; 58,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42,44; 61,64</t>
+          <t>44,44; 62,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,03; 52,25</t>
+          <t>36,55; 52,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28,29; 71,73</t>
+          <t>55,97; 73,04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,01; 65,12</t>
+          <t>49,4; 65,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,55; 58,57</t>
+          <t>37,89; 59,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,91; 68,16</t>
+          <t>47,89; 69,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71,11; 86,81</t>
+          <t>69,89; 85,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,49; 62,18</t>
+          <t>40,35; 61,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,53; 75,04</t>
+          <t>48,68; 73,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,71; 79,31</t>
+          <t>54,26; 78,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,36; 78,03</t>
+          <t>65,22; 79,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,0; 61,98</t>
+          <t>47,92; 61,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,85; 63,33</t>
+          <t>46,23; 62,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,33; 69,44</t>
+          <t>54,71; 69,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,86; 80,85</t>
+          <t>69,79; 80,47</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,26; 48,55</t>
+          <t>38,46; 48,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,42; 52,4</t>
+          <t>41,03; 52,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,98; 49,07</t>
+          <t>38,13; 49,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56,08; 67,1</t>
+          <t>55,96; 66,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,37; 57,55</t>
+          <t>44,12; 57,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,92; 64,17</t>
+          <t>49,47; 63,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,8; 66,93</t>
+          <t>53,42; 66,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,76; 68,22</t>
+          <t>62,92; 71,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42,3; 49,9</t>
+          <t>41,73; 49,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,55; 55,41</t>
+          <t>47,09; 55,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,73; 54,37</t>
+          <t>45,54; 54,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,36; 65,77</t>
+          <t>60,51; 67,9</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>34035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32570</t>
+          <t>36769</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64116</t>
+          <t>70804</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9092; 24302</t>
+          <t>9042; 23775</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19744; 36053</t>
+          <t>20100; 36285</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15546; 30908</t>
+          <t>13879; 29990</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22189; 40788</t>
+          <t>24493; 44518</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8465; 19509</t>
+          <t>8715; 19004</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12669; 24695</t>
+          <t>12747; 25490</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8217; 19380</t>
+          <t>8161; 18955</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27003; 38982</t>
+          <t>30122; 42308</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20829; 38920</t>
+          <t>20230; 39451</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35435; 57687</t>
+          <t>37071; 58249</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27511; 46492</t>
+          <t>26911; 45809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52715; 75066</t>
+          <t>59125; 83543</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60420</t>
+          <t>77106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>63153</t>
+          <t>68591</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>123572</t>
+          <t>145697</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50884; 75509</t>
+          <t>51533; 75310</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36341; 55512</t>
+          <t>37247; 56212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32161; 52714</t>
+          <t>32173; 53128</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49277; 71561</t>
+          <t>64446; 89997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17103; 31267</t>
+          <t>16789; 30938</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27493; 43532</t>
+          <t>27101; 43788</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21968; 37123</t>
+          <t>21642; 36486</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54660; 70983</t>
+          <t>59819; 76671</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72946; 102304</t>
+          <t>73780; 101733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70292; 95761</t>
+          <t>69946; 95123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57892; 84439</t>
+          <t>59183; 85100</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>108539; 136881</t>
+          <t>130221; 160449</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>41066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45729</t>
+          <t>49419</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82252</t>
+          <t>90484</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36584; 58302</t>
+          <t>36204; 57948</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32084; 52053</t>
+          <t>32708; 51107</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26694; 47023</t>
+          <t>26922; 47366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28540; 43525</t>
+          <t>31051; 49914</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23776; 36663</t>
+          <t>22990; 36446</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21537; 36340</t>
+          <t>21305; 36330</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34068; 49516</t>
+          <t>34346; 49488</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18207; 72813</t>
+          <t>42577; 55972</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64418; 90022</t>
+          <t>65173; 92193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56254; 81693</t>
+          <t>58901; 82837</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64684; 91272</t>
+          <t>63838; 91323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43053; 109154</t>
+          <t>78123; 101948</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81476</t>
+          <t>85008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>72871</t>
+          <t>77953</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>154347</t>
+          <t>162962</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67173; 89251</t>
+          <t>67695; 90076</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28288; 45332</t>
+          <t>29331; 46314</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41472; 60260</t>
+          <t>42341; 61011</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71844; 87701</t>
+          <t>75555; 92623</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35858; 55059</t>
+          <t>35734; 54647</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31107; 48096</t>
+          <t>31205; 46887</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36151; 52410</t>
+          <t>35857; 52084</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58555; 81070</t>
+          <t>70010; 84897</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>108283; 139823</t>
+          <t>108102; 138533</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64873; 89614</t>
+          <t>65415; 88841</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83938; 107273</t>
+          <t>84526; 107946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>139071; 165682</t>
+          <t>150374; 173364</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209966</t>
+          <t>237215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>214322</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>424288</t>
+          <t>469947</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>185412; 229307</t>
+          <t>181641; 228714</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>134651; 170371</t>
+          <t>133393; 169246</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132941; 171739</t>
+          <t>133469; 171833</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>190398; 227815</t>
+          <t>215437; 255905</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>97668; 126680</t>
+          <t>97113; 126572</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>107731; 138490</t>
+          <t>106769; 137870</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>116377; 144767</t>
+          <t>115538; 144165</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>151457; 241655</t>
+          <t>217276; 247807</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>292908; 345489</t>
+          <t>288922; 342872</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>251828; 299706</t>
+          <t>254735; 302557</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258995; 307871</t>
+          <t>257887; 306843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>349388; 456275</t>
+          <t>441934; 495872</t>
         </is>
       </c>
     </row>
